--- a/public/sap-reporting/expansion-150-downloads/EXT-FI27-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI27-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R41eeeee5be0d44d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R2c3a213cad074aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R5e966374c6664855"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R07b414b6e9f64f39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rb5be4e1cdd23429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R7fa0845535ab4a95"/>
   </x:sheets>
 </x:workbook>
 </file>
